--- a/conf/dataset.xlsx
+++ b/conf/dataset.xlsx
@@ -4,13 +4,16 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14508" windowHeight="13500"/>
+    <workbookView windowWidth="10668" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$103</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -172,7 +175,7 @@
     <t>BBH</t>
   </si>
   <si>
-    <t>Boolean_expressions</t>
+    <t>boolean_expressions</t>
   </si>
   <si>
     <t>Boolean expressions</t>
@@ -1416,7 +1419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:F103"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
@@ -1445,7 +1448,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" hidden="1" spans="1:6">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1465,7 +1468,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" hidden="1" spans="1:6">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1485,7 +1488,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" hidden="1" spans="1:6">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1505,7 +1508,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" hidden="1" spans="1:6">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1525,7 +1528,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" hidden="1" spans="1:6">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1545,7 +1548,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" hidden="1" spans="1:6">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1565,7 +1568,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" hidden="1" spans="1:6">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1585,7 +1588,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" hidden="1" spans="1:6">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1605,7 +1608,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" hidden="1" spans="1:6">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1625,7 +1628,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" hidden="1" spans="1:6">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1645,7 +1648,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" hidden="1" spans="1:6">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1665,7 +1668,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" hidden="1" spans="1:6">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1685,7 +1688,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" hidden="1" spans="1:6">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1705,7 +1708,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" hidden="1" spans="1:6">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1725,7 +1728,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" hidden="1" spans="1:6">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1745,7 +1748,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" hidden="1" spans="1:6">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1765,7 +1768,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" hidden="1" spans="1:6">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1785,7 +1788,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" hidden="1" spans="1:6">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1805,7 +1808,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" hidden="1" spans="1:6">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1825,7 +1828,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" hidden="1" spans="1:6">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1845,7 +1848,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" hidden="1" spans="1:6">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1865,7 +1868,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" hidden="1" spans="1:6">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1885,7 +1888,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" hidden="1" spans="1:6">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2445,7 +2448,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" hidden="1" spans="1:6">
       <c r="A52">
         <v>51</v>
       </c>
@@ -2465,7 +2468,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" hidden="1" spans="1:6">
       <c r="A53">
         <v>52</v>
       </c>
@@ -2485,7 +2488,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
+    <row r="54" hidden="1" spans="1:6">
       <c r="A54">
         <v>53</v>
       </c>
@@ -2505,7 +2508,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" hidden="1" spans="1:6">
       <c r="A55">
         <v>54</v>
       </c>
@@ -2525,7 +2528,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
+    <row r="56" hidden="1" spans="1:6">
       <c r="A56">
         <v>55</v>
       </c>
@@ -2545,7 +2548,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
+    <row r="57" hidden="1" spans="1:6">
       <c r="A57">
         <v>56</v>
       </c>
@@ -2565,7 +2568,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
+    <row r="58" hidden="1" spans="1:6">
       <c r="A58">
         <v>57</v>
       </c>
@@ -2585,7 +2588,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
+    <row r="59" hidden="1" spans="1:6">
       <c r="A59">
         <v>58</v>
       </c>
@@ -2605,7 +2608,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" hidden="1" spans="1:6">
       <c r="A60">
         <v>59</v>
       </c>
@@ -2625,7 +2628,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="61" spans="1:6">
+    <row r="61" hidden="1" spans="1:6">
       <c r="A61">
         <v>60</v>
       </c>
@@ -2645,7 +2648,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="62" spans="1:6">
+    <row r="62" hidden="1" spans="1:6">
       <c r="A62">
         <v>61</v>
       </c>
@@ -2665,7 +2668,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:6">
+    <row r="63" hidden="1" spans="1:6">
       <c r="A63">
         <v>62</v>
       </c>
@@ -2685,7 +2688,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="1:6">
+    <row r="64" hidden="1" spans="1:6">
       <c r="A64">
         <v>63</v>
       </c>
@@ -2705,7 +2708,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" hidden="1" spans="1:6">
       <c r="A65">
         <v>64</v>
       </c>
@@ -2725,7 +2728,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" hidden="1" spans="1:6">
       <c r="A66">
         <v>65</v>
       </c>
@@ -2745,7 +2748,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" hidden="1" spans="1:6">
       <c r="A67">
         <v>66</v>
       </c>
@@ -2765,7 +2768,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" hidden="1" spans="1:6">
       <c r="A68">
         <v>67</v>
       </c>
@@ -2785,7 +2788,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" hidden="1" spans="1:6">
       <c r="A69">
         <v>68</v>
       </c>
@@ -2805,7 +2808,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" hidden="1" spans="1:6">
       <c r="A70">
         <v>69</v>
       </c>
@@ -2825,7 +2828,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
+    <row r="71" hidden="1" spans="1:6">
       <c r="A71">
         <v>70</v>
       </c>
@@ -2845,7 +2848,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" hidden="1" spans="1:6">
       <c r="A72">
         <v>71</v>
       </c>
@@ -2865,7 +2868,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" hidden="1" spans="1:6">
       <c r="A73">
         <v>72</v>
       </c>
@@ -2885,7 +2888,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" hidden="1" spans="1:6">
       <c r="A74">
         <v>73</v>
       </c>
@@ -2905,7 +2908,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" hidden="1" spans="1:6">
       <c r="A75">
         <v>74</v>
       </c>
@@ -2925,7 +2928,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" hidden="1" spans="1:6">
       <c r="A76">
         <v>75</v>
       </c>
@@ -2945,7 +2948,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77" hidden="1" spans="1:6">
       <c r="A77">
         <v>76</v>
       </c>
@@ -2965,7 +2968,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="78" spans="1:6">
+    <row r="78" hidden="1" spans="1:6">
       <c r="A78">
         <v>77</v>
       </c>
@@ -2985,7 +2988,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" hidden="1" spans="1:6">
       <c r="A79">
         <v>78</v>
       </c>
@@ -3005,7 +3008,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" hidden="1" spans="1:6">
       <c r="A80">
         <v>79</v>
       </c>
@@ -3025,7 +3028,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" hidden="1" spans="1:6">
       <c r="A81">
         <v>80</v>
       </c>
@@ -3045,7 +3048,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82" hidden="1" spans="1:6">
       <c r="A82">
         <v>81</v>
       </c>
@@ -3065,7 +3068,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" hidden="1" spans="1:6">
       <c r="A83">
         <v>82</v>
       </c>
@@ -3085,7 +3088,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" hidden="1" spans="1:6">
       <c r="A84">
         <v>83</v>
       </c>
@@ -3105,7 +3108,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" hidden="1" spans="1:6">
       <c r="A85">
         <v>84</v>
       </c>
@@ -3125,7 +3128,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" hidden="1" spans="1:6">
       <c r="A86">
         <v>85</v>
       </c>
@@ -3145,7 +3148,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" hidden="1" spans="1:6">
       <c r="A87">
         <v>86</v>
       </c>
@@ -3165,7 +3168,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" hidden="1" spans="1:6">
       <c r="A88">
         <v>87</v>
       </c>
@@ -3185,7 +3188,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" hidden="1" spans="1:6">
       <c r="A89">
         <v>88</v>
       </c>
@@ -3205,7 +3208,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" hidden="1" spans="1:6">
       <c r="A90">
         <v>89</v>
       </c>
@@ -3225,7 +3228,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="91" spans="1:6">
+    <row r="91" hidden="1" spans="1:6">
       <c r="A91">
         <v>90</v>
       </c>
@@ -3245,7 +3248,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" hidden="1" spans="1:6">
       <c r="A92">
         <v>91</v>
       </c>
@@ -3265,7 +3268,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" hidden="1" spans="1:6">
       <c r="A93">
         <v>92</v>
       </c>
@@ -3285,7 +3288,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="94" spans="1:6">
+    <row r="94" hidden="1" spans="1:6">
       <c r="A94">
         <v>93</v>
       </c>
@@ -3305,7 +3308,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" hidden="1" spans="1:6">
       <c r="A95">
         <v>94</v>
       </c>
@@ -3325,7 +3328,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" hidden="1" spans="1:6">
       <c r="A96">
         <v>95</v>
       </c>
@@ -3345,7 +3348,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
+    <row r="97" hidden="1" spans="1:6">
       <c r="A97">
         <v>96</v>
       </c>
@@ -3365,7 +3368,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="98" spans="1:6">
+    <row r="98" hidden="1" spans="1:6">
       <c r="A98">
         <v>97</v>
       </c>
@@ -3385,7 +3388,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="99" spans="1:6">
+    <row r="99" hidden="1" spans="1:6">
       <c r="A99">
         <v>98</v>
       </c>
@@ -3405,7 +3408,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="100" spans="1:6">
+    <row r="100" hidden="1" spans="1:6">
       <c r="A100">
         <v>99</v>
       </c>
@@ -3425,7 +3428,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="101" spans="1:6">
+    <row r="101" hidden="1" spans="1:6">
       <c r="A101">
         <v>100</v>
       </c>
@@ -3445,7 +3448,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="102" spans="1:6">
+    <row r="102" hidden="1" spans="1:6">
       <c r="A102">
         <v>101</v>
       </c>
@@ -3465,7 +3468,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="103" spans="1:6">
+    <row r="103" hidden="1" spans="1:6">
       <c r="A103">
         <v>102</v>
       </c>
@@ -3486,6 +3489,14 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F103" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="BBH"/>
+      </filters>
+    </filterColumn>
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/conf/dataset.xlsx
+++ b/conf/dataset.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="10668" windowHeight="9180"/>
+    <workbookView windowWidth="22188" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1419,16 +1419,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:F103"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetPr/>
+  <dimension ref="A1:G103"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="49" customWidth="1"/>
     <col min="4" max="4" width="24.4444444444444" customWidth="1"/>
     <col min="5" max="5" width="18.6666666666667" customWidth="1"/>
+    <col min="7" max="7" width="21.1111111111111" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1447,8 +1448,9 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" hidden="1" spans="1:6">
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1468,7 +1470,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" hidden="1" spans="1:6">
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1488,7 +1490,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" hidden="1" spans="1:6">
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1508,7 +1510,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" hidden="1" spans="1:6">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1528,7 +1530,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" hidden="1" spans="1:6">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1548,7 +1550,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" hidden="1" spans="1:6">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1568,7 +1570,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" hidden="1" spans="1:6">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1588,7 +1590,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" hidden="1" spans="1:6">
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1608,7 +1610,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" hidden="1" spans="1:6">
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1628,7 +1630,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" hidden="1" spans="1:6">
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1648,7 +1650,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" hidden="1" spans="1:6">
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1668,7 +1670,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" hidden="1" spans="1:6">
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1688,7 +1690,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" hidden="1" spans="1:6">
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1708,7 +1710,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" hidden="1" spans="1:6">
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1728,7 +1730,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" hidden="1" spans="1:6">
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1748,7 +1750,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" hidden="1" spans="1:6">
+    <row r="17" spans="1:6">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1768,7 +1770,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" hidden="1" spans="1:6">
+    <row r="18" spans="1:6">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1788,7 +1790,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" hidden="1" spans="1:6">
+    <row r="19" spans="1:6">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1808,7 +1810,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" hidden="1" spans="1:6">
+    <row r="20" spans="1:6">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1828,7 +1830,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" hidden="1" spans="1:6">
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1848,7 +1850,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" hidden="1" spans="1:6">
+    <row r="22" spans="1:6">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1868,7 +1870,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" hidden="1" spans="1:6">
+    <row r="23" spans="1:6">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1888,7 +1890,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" hidden="1" spans="1:6">
+    <row r="24" spans="1:6">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2448,7 +2450,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" hidden="1" spans="1:6">
+    <row r="52" spans="1:6">
       <c r="A52">
         <v>51</v>
       </c>
@@ -2468,7 +2470,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" hidden="1" spans="1:6">
+    <row r="53" spans="1:6">
       <c r="A53">
         <v>52</v>
       </c>
@@ -2488,7 +2490,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="54" hidden="1" spans="1:6">
+    <row r="54" spans="1:6">
       <c r="A54">
         <v>53</v>
       </c>
@@ -2508,7 +2510,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="55" hidden="1" spans="1:6">
+    <row r="55" spans="1:6">
       <c r="A55">
         <v>54</v>
       </c>
@@ -2528,7 +2530,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="56" hidden="1" spans="1:6">
+    <row r="56" spans="1:6">
       <c r="A56">
         <v>55</v>
       </c>
@@ -2548,7 +2550,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" hidden="1" spans="1:6">
+    <row r="57" spans="1:6">
       <c r="A57">
         <v>56</v>
       </c>
@@ -2568,7 +2570,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" hidden="1" spans="1:6">
+    <row r="58" spans="1:6">
       <c r="A58">
         <v>57</v>
       </c>
@@ -2588,7 +2590,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" hidden="1" spans="1:6">
+    <row r="59" spans="1:6">
       <c r="A59">
         <v>58</v>
       </c>
@@ -2608,7 +2610,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" hidden="1" spans="1:6">
+    <row r="60" spans="1:6">
       <c r="A60">
         <v>59</v>
       </c>
@@ -2628,7 +2630,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="61" hidden="1" spans="1:6">
+    <row r="61" spans="1:6">
       <c r="A61">
         <v>60</v>
       </c>
@@ -2648,7 +2650,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="62" hidden="1" spans="1:6">
+    <row r="62" spans="1:6">
       <c r="A62">
         <v>61</v>
       </c>
@@ -2668,7 +2670,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" hidden="1" spans="1:6">
+    <row r="63" spans="1:6">
       <c r="A63">
         <v>62</v>
       </c>
@@ -2688,7 +2690,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" hidden="1" spans="1:6">
+    <row r="64" spans="1:6">
       <c r="A64">
         <v>63</v>
       </c>
@@ -2708,7 +2710,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="65" hidden="1" spans="1:6">
+    <row r="65" spans="1:6">
       <c r="A65">
         <v>64</v>
       </c>
@@ -2728,7 +2730,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="66" hidden="1" spans="1:6">
+    <row r="66" spans="1:6">
       <c r="A66">
         <v>65</v>
       </c>
@@ -2748,7 +2750,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="67" hidden="1" spans="1:6">
+    <row r="67" spans="1:6">
       <c r="A67">
         <v>66</v>
       </c>
@@ -2768,7 +2770,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="68" hidden="1" spans="1:6">
+    <row r="68" spans="1:6">
       <c r="A68">
         <v>67</v>
       </c>
@@ -2788,7 +2790,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="69" hidden="1" spans="1:6">
+    <row r="69" spans="1:6">
       <c r="A69">
         <v>68</v>
       </c>
@@ -2808,7 +2810,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="70" hidden="1" spans="1:6">
+    <row r="70" spans="1:6">
       <c r="A70">
         <v>69</v>
       </c>
@@ -2828,7 +2830,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="71" hidden="1" spans="1:6">
+    <row r="71" spans="1:6">
       <c r="A71">
         <v>70</v>
       </c>
@@ -2848,7 +2850,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="72" hidden="1" spans="1:6">
+    <row r="72" spans="1:6">
       <c r="A72">
         <v>71</v>
       </c>
@@ -2868,7 +2870,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="73" hidden="1" spans="1:6">
+    <row r="73" spans="1:6">
       <c r="A73">
         <v>72</v>
       </c>
@@ -2888,7 +2890,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="74" hidden="1" spans="1:6">
+    <row r="74" spans="1:6">
       <c r="A74">
         <v>73</v>
       </c>
@@ -2908,7 +2910,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="75" hidden="1" spans="1:6">
+    <row r="75" spans="1:6">
       <c r="A75">
         <v>74</v>
       </c>
@@ -2928,7 +2930,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="76" hidden="1" spans="1:6">
+    <row r="76" spans="1:6">
       <c r="A76">
         <v>75</v>
       </c>
@@ -2948,7 +2950,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" hidden="1" spans="1:6">
+    <row r="77" spans="1:6">
       <c r="A77">
         <v>76</v>
       </c>
@@ -2968,7 +2970,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="78" hidden="1" spans="1:6">
+    <row r="78" spans="1:6">
       <c r="A78">
         <v>77</v>
       </c>
@@ -2988,7 +2990,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="79" hidden="1" spans="1:6">
+    <row r="79" spans="1:6">
       <c r="A79">
         <v>78</v>
       </c>
@@ -3008,7 +3010,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="80" hidden="1" spans="1:6">
+    <row r="80" spans="1:6">
       <c r="A80">
         <v>79</v>
       </c>
@@ -3028,7 +3030,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="81" hidden="1" spans="1:6">
+    <row r="81" spans="1:6">
       <c r="A81">
         <v>80</v>
       </c>
@@ -3048,7 +3050,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="82" hidden="1" spans="1:6">
+    <row r="82" spans="1:6">
       <c r="A82">
         <v>81</v>
       </c>
@@ -3068,7 +3070,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="83" hidden="1" spans="1:6">
+    <row r="83" spans="1:6">
       <c r="A83">
         <v>82</v>
       </c>
@@ -3088,7 +3090,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="84" hidden="1" spans="1:6">
+    <row r="84" spans="1:6">
       <c r="A84">
         <v>83</v>
       </c>
@@ -3108,7 +3110,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="85" hidden="1" spans="1:6">
+    <row r="85" spans="1:6">
       <c r="A85">
         <v>84</v>
       </c>
@@ -3128,7 +3130,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="86" hidden="1" spans="1:6">
+    <row r="86" spans="1:6">
       <c r="A86">
         <v>85</v>
       </c>
@@ -3148,7 +3150,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="87" hidden="1" spans="1:6">
+    <row r="87" spans="1:6">
       <c r="A87">
         <v>86</v>
       </c>
@@ -3168,7 +3170,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="88" hidden="1" spans="1:6">
+    <row r="88" spans="1:6">
       <c r="A88">
         <v>87</v>
       </c>
@@ -3188,7 +3190,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="89" hidden="1" spans="1:6">
+    <row r="89" spans="1:6">
       <c r="A89">
         <v>88</v>
       </c>
@@ -3208,7 +3210,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="90" hidden="1" spans="1:6">
+    <row r="90" spans="1:6">
       <c r="A90">
         <v>89</v>
       </c>
@@ -3228,7 +3230,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="91" hidden="1" spans="1:6">
+    <row r="91" spans="1:6">
       <c r="A91">
         <v>90</v>
       </c>
@@ -3248,7 +3250,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="92" hidden="1" spans="1:6">
+    <row r="92" spans="1:6">
       <c r="A92">
         <v>91</v>
       </c>
@@ -3268,7 +3270,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="93" hidden="1" spans="1:6">
+    <row r="93" spans="1:6">
       <c r="A93">
         <v>92</v>
       </c>
@@ -3288,7 +3290,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="94" hidden="1" spans="1:6">
+    <row r="94" spans="1:6">
       <c r="A94">
         <v>93</v>
       </c>
@@ -3308,7 +3310,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="95" hidden="1" spans="1:6">
+    <row r="95" spans="1:6">
       <c r="A95">
         <v>94</v>
       </c>
@@ -3328,7 +3330,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="96" hidden="1" spans="1:6">
+    <row r="96" spans="1:6">
       <c r="A96">
         <v>95</v>
       </c>
@@ -3348,7 +3350,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="97" hidden="1" spans="1:6">
+    <row r="97" spans="1:6">
       <c r="A97">
         <v>96</v>
       </c>
@@ -3368,7 +3370,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="98" hidden="1" spans="1:6">
+    <row r="98" spans="1:6">
       <c r="A98">
         <v>97</v>
       </c>
@@ -3388,7 +3390,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="99" hidden="1" spans="1:6">
+    <row r="99" spans="1:6">
       <c r="A99">
         <v>98</v>
       </c>
@@ -3408,7 +3410,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="100" hidden="1" spans="1:6">
+    <row r="100" spans="1:6">
       <c r="A100">
         <v>99</v>
       </c>
@@ -3428,7 +3430,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="101" hidden="1" spans="1:6">
+    <row r="101" spans="1:6">
       <c r="A101">
         <v>100</v>
       </c>
@@ -3448,7 +3450,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="102" hidden="1" spans="1:6">
+    <row r="102" spans="1:6">
       <c r="A102">
         <v>101</v>
       </c>
@@ -3468,7 +3470,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="103" hidden="1" spans="1:6">
+    <row r="103" spans="1:6">
       <c r="A103">
         <v>102</v>
       </c>
@@ -3490,11 +3492,6 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F103" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="BBH"/>
-      </filters>
-    </filterColumn>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
